--- a/data/employees/EMP008/AST-EMP008-06.xlsx
+++ b/data/employees/EMP008/AST-EMP008-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project Resource Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,210 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Project Resource Tracker - Jamie Brown (Engineering)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Jamie Brown | Role: Engineer | Location: Austin | Date: 2025-01-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp008 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>70</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp008 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>67</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Project</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Milestone</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Resources</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp008 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>71</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Proj Alpha</t>
+          <t>EMP008</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M1 - Design</t>
+          <t>Ast Emp008 06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Team A</t>
+          <t>2026-W04</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2025-01-29</t>
-        </is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>80</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>4</v>
+          <t>Section 1: Data quality remediation. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Proj Beta</t>
+          <t>EMP008</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M2 - Build</t>
+          <t>Ast Emp008 06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Team B</t>
+          <t>2026-W05</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2025-03-20</t>
-        </is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>90</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Delayed</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>6</v>
+          <t>Section 1: Quarterly delivery milestones. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Proj Gamma</t>
+          <t>EMP008</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M1 - Design</t>
+          <t>Ast Emp008 06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Team C</t>
+          <t>2026-W06</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2025-04-01</t>
-        </is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>60</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>On Track</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>3</v>
+          <t>Section 1: Customer escalation analysis. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Proj Delta</t>
+          <t>EMP008</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M3 - Test</t>
+          <t>Ast Emp008 06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Team A</t>
+          <t>2026-W07</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
-        </is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>90</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>At Risk</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>5</v>
+          <t>Section 1: Quarterly delivery milestones. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp008 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>92</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp008 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>69</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp008 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>61</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp008 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>71</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp008 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>69</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp008 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>83</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp008 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>66</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp008 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>68</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp008 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>86</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp008 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>97</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp008 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>77</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp008 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>96</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp008 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>86</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp008 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>96</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp008 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>60</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp008 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>78</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp008 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>69</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP008 contributes to ast emp008 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>